--- a/ebegu-server/src/main/resources/reporting/ZahlungAuftrag.xlsx
+++ b/ebegu-server/src/main/resources/reporting/ZahlungAuftrag.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enja\IdeaProjects\ebegu\ebegu-server\src\main\resources\reporting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aese\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169EE4C8-B325-47C0-A0B1-52A18322B93E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C383A4BB-EE3B-4777-8604-F320BBDE4BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Totals" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>{institution}</t>
   </si>
@@ -124,12 +124,6 @@
     <t>{betreuungsangebotTypTitle}</t>
   </si>
   <si>
-    <t>{institutionIdTitle}</t>
-  </si>
-  <si>
-    <t>{institutionId}</t>
-  </si>
-  <si>
     <t>{traegerschaftTitle}</t>
   </si>
   <si>
@@ -190,16 +184,16 @@
     <t>{repeatZahlungTotalsRow}</t>
   </si>
   <si>
-    <t>{antragstellerTitle}</t>
-  </si>
-  <si>
-    <t>{antragsteller}</t>
-  </si>
-  <si>
-    <t>{antragsteller2Title}</t>
-  </si>
-  <si>
-    <t>{antragsteller2}</t>
+    <t>{institutionTitle}{antragstellerTitle}</t>
+  </si>
+  <si>
+    <t>{institution}{antragsteller}</t>
+  </si>
+  <si>
+    <t>{institutionIdTitle}{antragsteller2Title}</t>
+  </si>
+  <si>
+    <t>{institutionId}{antragsteller2}</t>
   </si>
 </sst>
 </file>
@@ -311,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -330,16 +324,12 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -356,17 +346,7 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -702,42 +682,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002696E7-1347-4331-86FF-AE08C25E0F9C}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="6" width="25.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
-    <col min="8" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="3" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-    </row>
-    <row r="2" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -745,7 +723,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -753,7 +731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -761,151 +739,127 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G6" s="16" t="s">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E7" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="16"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="18"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N7" s="2" t="s">
+      <c r="J9" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="O8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G6:N6"/>
+    <mergeCell ref="E7:L7"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8 P8:XFD8 D8:G8 A9:D999992 G9:XFD999992 I8:N8 E8:F999992">
-    <cfRule type="expression" dxfId="6" priority="7">
+  <conditionalFormatting sqref="A9">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>$K9="X"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9 D9:L9 N9:XFD9 A10:XFD999993">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>#REF!="X"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8">
-    <cfRule type="expression" dxfId="5" priority="5">
-      <formula>#REF!="X"</formula>
+  <conditionalFormatting sqref="C9:D9">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$K9="X"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>$M8="X"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8:F8">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>$M8="X"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O8">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$M8="X"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F999992">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>#REF!="X"</formula>
+  <conditionalFormatting sqref="M9">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$K9="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -933,20 +887,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1030,7 +984,7 @@
       <c r="E8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="6" t="s">
